--- a/artfynd/A 3838-2024 artfynd.xlsx
+++ b/artfynd/A 3838-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3838-2024 artfynd.xlsx
+++ b/artfynd/A 3838-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68268930</v>
+        <v>6760391</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Överammer / 2 km N /, Jmt</t>
+          <t>öVERAMMER (19G2b01), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547560.8371137964</v>
+        <v>547561</v>
       </c>
       <c r="R2" t="n">
-        <v>7011665.975275867</v>
+        <v>7011666</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -746,34 +738,19 @@
           <t>Ragunda</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Z-Rag-1312</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>1989-06-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-06-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens naturvärdesobjekt. Allmän-riklig (3) / OBJ.AREA:11,4 ha. ÖVERAMMER (19G2b01) Koordinat O1507112, N7013500 (±50m). Kopia till floraväkteriet.</t>
+          <t>190621011 / CYPR CAL / Allmän-riklig (3)  / OBJ.AREA:11,4 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +765,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -798,56 +775,51 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111670773</v>
+        <v>110242029</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckmansmyran, V, Jmt</t>
+          <t>Bäckmanstorpet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547655</v>
+        <v>547599</v>
       </c>
       <c r="R3" t="n">
-        <v>7011712</v>
+        <v>7011832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,15 +866,213 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111670773</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bäckmansmyran, V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>547654</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7011712</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111670743</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bäckmansmyran, V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547504</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7011748</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3838-2024 artfynd.xlsx
+++ b/artfynd/A 3838-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6760391</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110242029</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111670773</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,8 +1093,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111670743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>